--- a/docs/oc-mensuales/suministro-de-combustibles/ago-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/ago-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35807,7 +35807,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36661,7 +36661,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36844,7 +36844,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37149,7 +37149,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37393,7 +37393,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37576,7 +37576,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37637,7 +37637,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37698,7 +37698,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37759,7 +37759,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38064,7 +38064,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38186,7 +38186,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38491,7 +38491,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39040,7 +39040,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39101,7 +39101,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39223,7 +39223,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39406,7 +39406,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39467,7 +39467,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39589,7 +39589,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39833,7 +39833,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39955,7 +39955,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40016,7 +40016,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40138,7 +40138,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40199,7 +40199,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40321,7 +40321,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40565,7 +40565,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40626,7 +40626,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40687,7 +40687,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40748,7 +40748,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40809,7 +40809,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40870,7 +40870,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40992,7 +40992,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41114,7 +41114,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41175,7 +41175,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41236,7 +41236,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41297,7 +41297,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41358,7 +41358,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41480,7 +41480,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41541,7 +41541,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41602,7 +41602,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41663,7 +41663,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41724,7 +41724,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41907,7 +41907,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41968,7 +41968,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42151,7 +42151,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42212,7 +42212,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42273,7 +42273,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42395,7 +42395,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42578,7 +42578,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42761,7 +42761,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42944,7 +42944,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43066,7 +43066,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43127,7 +43127,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43188,7 +43188,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43249,7 +43249,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43310,7 +43310,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43493,7 +43493,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43615,7 +43615,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43676,7 +43676,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43737,7 +43737,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43798,7 +43798,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
